--- a/Data/FlightPlan/FPL_16AUG26.xlsx
+++ b/Data/FlightPlan/FPL_16AUG26.xlsx
@@ -335,381 +335,384 @@
     <t>14:50</t>
   </si>
   <si>
+    <t>17:52</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>17:51</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:17</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>VN-A525</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:08</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>14:28</t>
+  </si>
+  <si>
+    <t>18:08</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>15:52</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:33</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>14:59</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
     <t>16:50</t>
   </si>
   <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:21</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>17:51</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:17</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A525</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>13:27</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:08</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:53</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:56</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>16:22</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>14:56</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>17:28</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>14:28</t>
-  </si>
-  <si>
-    <t>18:08</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>12:56</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>15:52</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:33</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:39</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:29</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>12:06</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>14:59</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
     <t>18:15</t>
   </si>
   <si>
@@ -1106,591 +1109,591 @@
     <t>17:19</t>
   </si>
   <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>15:36</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>06:37</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:21</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>09:29</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>07:08</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:27</t>
+  </si>
+  <si>
+    <t>13:12</t>
+  </si>
+  <si>
+    <t>16:14</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>06:58</t>
+  </si>
+  <si>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>14:52</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>13:31</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>14:39</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>15:01</t>
+  </si>
+  <si>
+    <t>16:39</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>09:32</t>
+  </si>
+  <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>19:34</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:13</t>
+  </si>
+  <si>
+    <t>13:39</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>11:59</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>10:51</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>10:06</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>16:51</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>10:58</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>07:09</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>11:12</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>16:34</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>16:52</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>18:23</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
     <t>04:30</t>
   </si>
   <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>09:28</t>
-  </si>
-  <si>
-    <t>15:36</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>10:56</t>
-  </si>
-  <si>
-    <t>13:02</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>18:16</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>05:10</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:21</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>09:29</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>07:08</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:27</t>
-  </si>
-  <si>
-    <t>13:12</t>
-  </si>
-  <si>
-    <t>16:14</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>10:46</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>14:37</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:02</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>17:01</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>10:24</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>13:53</t>
-  </si>
-  <si>
-    <t>16:48</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>06:58</t>
-  </si>
-  <si>
-    <t>10:41</t>
-  </si>
-  <si>
-    <t>14:52</t>
-  </si>
-  <si>
-    <t>16:42</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>16:13</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>13:31</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>14:53</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>14:39</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>08:04</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>15:01</t>
-  </si>
-  <si>
-    <t>16:39</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>06:31</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>10:29</t>
-  </si>
-  <si>
-    <t>16:23</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>14:22</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>09:32</t>
-  </si>
-  <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>10:04</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>19:34</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:13</t>
-  </si>
-  <si>
-    <t>13:39</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:54</t>
-  </si>
-  <si>
-    <t>11:59</t>
-  </si>
-  <si>
-    <t>13:59</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>08:26</t>
-  </si>
-  <si>
-    <t>10:51</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:06</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>16:51</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>10:58</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>09:44</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>15:11</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>07:09</t>
-  </si>
-  <si>
-    <t>08:37</t>
-  </si>
-  <si>
-    <t>11:12</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>16:34</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>22:03</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>16:52</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>18:23</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1751,7 +1754,7 @@
     <t>Total Record(s): 445</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 16, 2026 16:42</t>
+    <t xml:space="preserve">Generated on  Aug 16, 2026 16:48</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5376,11 +5379,11 @@
         <v>167</v>
       </c>
       <c t="s" r="K103" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5407,10 +5410,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="K104" s="7">
         <v>141</v>
@@ -5444,10 +5447,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5477,10 +5480,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5513,7 +5516,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5525,7 +5528,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>31</v>
@@ -5533,7 +5536,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5548,7 +5551,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5563,12 +5566,12 @@
         <v>53</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5583,7 +5586,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5618,7 +5621,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5630,7 +5633,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>174</v>
@@ -5638,7 +5641,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5653,7 +5656,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5686,7 +5689,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5698,7 +5701,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>83</v>
@@ -5734,7 +5737,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5746,15 +5749,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5769,7 +5772,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5781,7 +5784,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>136</v>
@@ -5789,7 +5792,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5804,7 +5807,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5826,7 +5829,7 @@
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5841,7 +5844,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5859,11 +5862,11 @@
         <v>109</v>
       </c>
       <c t="s" r="K118" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5878,7 +5881,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5890,17 +5893,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="K119" s="7">
         <v>77</v>
       </c>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5915,7 +5918,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5927,17 +5930,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>142</v>
       </c>
       <c t="s" r="K120" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5952,7 +5955,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5964,7 +5967,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>158</v>
@@ -6000,7 +6003,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6012,15 +6015,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -6035,7 +6038,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6047,15 +6050,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6070,7 +6073,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6090,7 +6093,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6105,7 +6108,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6125,7 +6128,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6140,7 +6143,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6152,10 +6155,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="K127" s="7">
         <v>80</v>
@@ -6177,7 +6180,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6189,13 +6192,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>78</v>
       </c>
       <c t="s" r="K128" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
@@ -6214,7 +6217,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6226,17 +6229,17 @@
         <v>72</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="K129" s="7">
         <v>206</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6251,7 +6254,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6263,17 +6266,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="K130" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6288,7 +6291,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6300,10 +6303,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -6336,7 +6339,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6371,7 +6374,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6386,12 +6389,12 @@
         <v>21</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6406,7 +6409,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6421,7 +6424,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6439,7 +6442,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6448,10 +6451,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>168</v>
@@ -6472,13 +6475,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>43</v>
@@ -6487,7 +6490,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6520,7 +6523,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6532,15 +6535,15 @@
         <v>191</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6555,7 +6558,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6567,7 +6570,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>228</v>
@@ -6575,7 +6578,7 @@
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6590,7 +6593,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6605,12 +6608,12 @@
         <v>90</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6625,7 +6628,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6637,15 +6640,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6660,7 +6663,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6669,13 +6672,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6693,13 +6696,13 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>16</v>
@@ -6708,7 +6711,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6741,7 +6744,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6761,7 +6764,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6776,7 +6779,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6796,7 +6799,7 @@
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6811,7 +6814,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6820,10 +6823,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>82</v>
@@ -6844,22 +6847,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6892,7 +6895,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6907,12 +6910,12 @@
         <v>120</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6927,7 +6930,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6942,12 +6945,12 @@
         <v>162</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6962,7 +6965,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6974,7 +6977,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>93</v>
@@ -6982,7 +6985,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6997,7 +7000,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7009,15 +7012,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7032,7 +7035,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7044,13 +7047,13 @@
         <v>43</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="K155" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
@@ -7069,7 +7072,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7084,7 +7087,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="K156" s="7">
         <v>153</v>
@@ -7106,7 +7109,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7118,10 +7121,10 @@
         <v>111</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="K157" s="7">
         <v>219</v>
@@ -7143,7 +7146,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -7158,14 +7161,14 @@
         <v>154</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="K158" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7195,7 +7198,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7207,10 +7210,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -7230,7 +7233,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7242,7 +7245,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>109</v>
@@ -7250,7 +7253,7 @@
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7265,7 +7268,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7280,7 +7283,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="K162" s="7">
         <v>95</v>
@@ -7302,7 +7305,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7317,7 +7320,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -7350,7 +7353,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7385,7 +7388,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7394,7 +7397,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>57</v>
@@ -7422,13 +7425,13 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>16</v>
@@ -7474,7 +7477,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7486,7 +7489,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>33</v>
@@ -7494,7 +7497,7 @@
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7509,7 +7512,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7518,10 +7521,10 @@
         <v>72</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>107</v>
@@ -7544,27 +7547,27 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>191</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7579,7 +7582,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7588,10 +7591,10 @@
         <v>191</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>78</v>
@@ -7612,13 +7615,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>72</v>
@@ -7660,7 +7663,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7672,15 +7675,15 @@
         <v>131</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7695,7 +7698,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7704,7 +7707,7 @@
         <v>131</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>126</v>
@@ -7715,7 +7718,7 @@
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7730,19 +7733,19 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>131</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>154</v>
@@ -7763,7 +7766,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7775,10 +7778,10 @@
         <v>63</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7811,7 +7814,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7823,13 +7826,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="K180" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
@@ -7848,7 +7851,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7857,10 +7860,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>139</v>
@@ -7883,19 +7886,19 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>174</v>
@@ -7903,7 +7906,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7918,7 +7921,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7927,13 +7930,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7951,13 +7954,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
@@ -7966,7 +7969,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7999,7 +8002,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8014,12 +8017,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8034,7 +8037,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8046,15 +8049,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8069,7 +8072,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8089,7 +8092,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8104,7 +8107,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8119,12 +8122,12 @@
         <v>105</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8139,7 +8142,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8174,7 +8177,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8186,10 +8189,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -8222,22 +8225,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -8257,7 +8260,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8269,7 +8272,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>165</v>
@@ -8279,7 +8282,7 @@
       </c>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8294,7 +8297,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8309,7 +8312,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -8327,7 +8330,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8336,13 +8339,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8375,13 +8378,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>16</v>
@@ -8395,7 +8398,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8410,7 +8413,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8419,13 +8422,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -8443,13 +8446,13 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>16</v>
@@ -8476,7 +8479,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8509,7 +8512,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8521,7 +8524,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>181</v>
@@ -8557,7 +8560,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8566,7 +8569,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I204" s="7">
         <v>225</v>
@@ -8577,7 +8580,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8592,13 +8595,13 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>43</v>
@@ -8612,7 +8615,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8627,7 +8630,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8639,7 +8642,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>49</v>
@@ -8653,14 +8656,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>836</v>
+        <v>780</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8669,13 +8672,13 @@
         <v>131</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>27</v>
+        <v>280</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>365</v>
+        <v>219</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8720,7 +8723,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>367</v>
@@ -8763,7 +8766,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8828,12 +8831,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8860,7 +8863,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>177</v>
@@ -8893,7 +8896,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>132</v>
@@ -8944,7 +8947,7 @@
         <v>371</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -9081,7 +9084,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>21</v>
@@ -9118,7 +9121,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>109</v>
@@ -9128,7 +9131,7 @@
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9155,10 +9158,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="K222" s="7">
         <v>167</v>
@@ -9192,13 +9195,13 @@
         <v>72</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>49</v>
       </c>
       <c t="s" r="K223" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
@@ -9229,17 +9232,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9266,7 +9269,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>28</v>
@@ -9318,7 +9321,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>19</v>
@@ -9350,7 +9353,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>149</v>
@@ -9382,13 +9385,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>142</v>
@@ -9469,17 +9472,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9503,10 +9506,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>381</v>
@@ -9537,7 +9540,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>56</v>
@@ -9577,10 +9580,10 @@
         <v>56</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>97</v>
@@ -9609,7 +9612,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>16</v>
@@ -9618,7 +9621,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9666,7 +9669,7 @@
         <v>386</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9701,7 +9704,7 @@
         <v>388</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9733,7 +9736,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>390</v>
@@ -9768,7 +9771,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>381</v>
@@ -9850,7 +9853,7 @@
       </c>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9877,7 +9880,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>95</v>
@@ -9887,7 +9890,7 @@
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9963,13 +9966,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>394</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9995,7 +9998,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>43</v>
@@ -10071,10 +10074,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -10106,17 +10109,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="K251" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10146,7 +10149,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -10226,7 +10229,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>53</v>
@@ -10258,13 +10261,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -10290,7 +10293,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>16</v>
@@ -10299,12 +10302,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10368,10 +10371,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -10416,7 +10419,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>194</v>
@@ -10454,7 +10457,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10483,10 +10486,10 @@
         <v>72</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>198</v>
@@ -10515,16 +10518,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10553,7 +10556,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>73</v>
@@ -10585,13 +10588,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>405</v>
@@ -10627,7 +10630,7 @@
         <v>406</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10707,7 +10710,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>390</v>
@@ -10739,7 +10742,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I271" s="7">
         <v>198</v>
@@ -10771,7 +10774,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>43</v>
@@ -10809,7 +10812,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>60</v>
@@ -10839,13 +10842,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>27</v>
@@ -10936,7 +10939,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10963,7 +10966,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>413</v>
@@ -11035,15 +11038,15 @@
         <v>124</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11070,7 +11073,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>96</v>
@@ -11106,7 +11109,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -11136,7 +11139,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>181</v>
@@ -11222,7 +11225,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -11254,7 +11257,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>122</v>
@@ -11289,7 +11292,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>75</v>
@@ -11324,15 +11327,15 @@
         <v>56</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11395,7 +11398,7 @@
         <v>178</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="K291" s="7">
         <v>179</v>
@@ -11668,7 +11671,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -11697,13 +11700,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>181</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11748,7 +11751,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>69</v>
@@ -11856,7 +11859,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11919,7 +11922,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>434</v>
@@ -11970,7 +11973,7 @@
         <v>371</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -12040,7 +12043,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -12072,7 +12075,7 @@
         <v>415</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>107</v>
@@ -12142,7 +12145,7 @@
         <v>415</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>425</v>
@@ -12226,7 +12229,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -12331,7 +12334,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -12366,7 +12369,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12399,7 +12402,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -12479,7 +12482,7 @@
         <v>441</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>172</v>
@@ -12514,10 +12517,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -12549,10 +12552,10 @@
         <v>441</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12630,7 +12633,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>138</v>
@@ -12673,7 +12676,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12748,10 +12751,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12783,7 +12786,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>431</v>
@@ -12861,7 +12864,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12961,14 +12964,14 @@
         <v>83</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="K341" s="7">
         <v>83</v>
       </c>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13010,15 +13013,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13053,7 +13056,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13153,14 +13156,14 @@
         <v>230</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c t="s" r="K347" s="7">
         <v>106</v>
       </c>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13265,13 +13268,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -13297,13 +13300,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>390</v>
@@ -13335,7 +13338,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>198</v>
@@ -13367,13 +13370,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>48</v>
@@ -13411,7 +13414,7 @@
         <v>466</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13510,7 +13513,7 @@
         <v>468</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13590,7 +13593,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>160</v>
@@ -13660,7 +13663,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>228</v>
@@ -13775,7 +13778,7 @@
       </c>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13802,7 +13805,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>25</v>
@@ -13812,7 +13815,7 @@
       </c>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -14025,10 +14028,10 @@
         <v>131</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="K374" s="7">
         <v>60</v>
@@ -14062,7 +14065,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>481</v>
@@ -14072,7 +14075,7 @@
       </c>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14159,7 +14162,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14221,10 +14224,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -14302,7 +14305,7 @@
         <v>441</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>225</v>
@@ -14337,7 +14340,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>198</v>
@@ -14345,7 +14348,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14372,7 +14375,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>70</v>
@@ -14410,7 +14413,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14439,20 +14442,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>174</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="K387" s="7">
         <v>80</v>
       </c>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14473,7 +14476,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
@@ -14562,7 +14565,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>227</v>
@@ -14672,10 +14675,10 @@
         <v>21</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="K394" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
@@ -14789,10 +14792,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14824,7 +14827,7 @@
         <v>212</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>93</v>
@@ -14862,7 +14865,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -14930,7 +14933,7 @@
         <v>176</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14957,7 +14960,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>186</v>
@@ -14987,7 +14990,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>16</v>
@@ -15111,7 +15114,7 @@
         <v>441</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>457</v>
@@ -15178,10 +15181,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J410" s="7">
         <v>167</v>
@@ -15210,13 +15213,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>128</v>
@@ -15334,10 +15337,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -15416,13 +15419,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -15448,16 +15451,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -15571,7 +15574,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -15603,7 +15606,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>93</v>
@@ -15638,10 +15641,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15709,7 +15712,7 @@
         <v>481</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15739,7 +15742,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>168</v>
@@ -15822,10 +15825,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -15857,10 +15860,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15890,7 +15893,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>205</v>
@@ -15926,7 +15929,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15971,10 +15974,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -16078,7 +16081,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>206</v>
@@ -16237,7 +16240,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16261,13 +16264,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I445" s="7">
         <v>75</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -16293,13 +16296,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>96</v>
@@ -16448,10 +16451,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -16480,10 +16483,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>55</v>
@@ -16512,7 +16515,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>43</v>
@@ -16556,7 +16559,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16588,7 +16591,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>467</v>
@@ -16624,7 +16627,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -16654,7 +16657,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>534</v>
@@ -16705,7 +16708,7 @@
         <v>470</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -16922,7 +16925,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I466" s="7">
         <v>189</v>
@@ -16954,13 +16957,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>91</v>
@@ -17030,7 +17033,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>545</v>
@@ -17078,15 +17081,15 @@
         <v>63</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
       <c t="s" r="M471" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="472" ht="14.25" customHeight="1">
@@ -17181,7 +17184,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I474" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J474" s="7">
         <v>81</v>
@@ -17214,7 +17217,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J475" s="7">
         <v>470</v>
@@ -17262,7 +17265,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>511</v>
@@ -17335,7 +17338,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -17367,7 +17370,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J480" s="7">
         <v>75</v>
@@ -17375,7 +17378,7 @@
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -17405,7 +17408,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J481" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -17440,7 +17443,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
@@ -17503,7 +17506,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J484" s="7">
         <v>86</v>
@@ -17559,7 +17562,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -17589,7 +17592,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -17624,7 +17627,7 @@
         <v>382</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -17699,7 +17702,7 @@
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
       <c t="s" r="M490" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="491" ht="14.25" customHeight="1">
@@ -17729,7 +17732,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -17771,7 +17774,7 @@
       </c>
       <c r="L492" s="7"/>
       <c t="s" r="M492" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
@@ -17804,11 +17807,11 @@
         <v>81</v>
       </c>
       <c t="s" r="K493" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L493" s="7"/>
       <c t="s" r="M493" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="494" ht="14.25" customHeight="1">
@@ -17850,7 +17853,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I495" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J495" s="7">
         <v>142</v>
@@ -17886,7 +17889,7 @@
         <v>426</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -18019,7 +18022,7 @@
         <v>13</v>
       </c>
       <c r="B501" s="7">
-        <v>780</v>
+        <v>836</v>
       </c>
       <c t="s" r="C501" s="7">
         <v>14</v>
@@ -18035,13 +18038,13 @@
         <v>131</v>
       </c>
       <c t="s" r="H501" s="8">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c t="s" r="I501" s="7">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c t="s" r="J501" s="7">
-        <v>219</v>
+        <v>560</v>
       </c>
       <c r="K501" s="7"/>
       <c r="L501" s="7"/>
@@ -18074,7 +18077,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F503" s="7">
         <v>320</v>
@@ -18083,10 +18086,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H503" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I503" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J503" s="7">
         <v>162</v>
@@ -18109,13 +18112,13 @@
       </c>
       <c r="D504" s="7"/>
       <c t="s" r="E504" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F504" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G504" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H504" s="8">
         <v>16</v>
@@ -18129,7 +18132,7 @@
       <c r="K504" s="7"/>
       <c r="L504" s="7"/>
       <c t="s" r="M504" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="505" ht="15" customHeight="1">
@@ -18144,7 +18147,7 @@
       </c>
       <c r="D505" s="7"/>
       <c t="s" r="E505" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F505" s="7">
         <v>320</v>
@@ -18156,15 +18159,15 @@
         <v>441</v>
       </c>
       <c t="s" r="I505" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J505" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K505" s="7"/>
       <c r="L505" s="7"/>
       <c t="s" r="M505" s="7">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="506" ht="14.25" customHeight="1">
@@ -18179,7 +18182,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F506" s="7">
         <v>320</v>
@@ -18191,15 +18194,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I506" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J506" s="7">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
       <c t="s" r="M506" s="7">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="507" ht="14.25" customHeight="1">
@@ -18214,7 +18217,7 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F507" s="7">
         <v>320</v>
@@ -18226,7 +18229,7 @@
         <v>193</v>
       </c>
       <c t="s" r="I507" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J507" s="7">
         <v>467</v>
@@ -18247,7 +18250,7 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F508" s="7">
         <v>320</v>
@@ -18280,7 +18283,7 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F509" s="7">
         <v>320</v>
@@ -18295,7 +18298,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J509" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="K509" s="7">
         <v>206</v>
@@ -18332,7 +18335,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F511" s="7">
         <v>330</v>
@@ -18344,7 +18347,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I511" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J511" s="7">
         <v>160</v>
@@ -18367,7 +18370,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F512" s="7">
         <v>330</v>
@@ -18387,7 +18390,7 @@
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
       <c t="s" r="M512" s="7">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="513" ht="14.25" customHeight="1">
@@ -18402,7 +18405,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F513" s="7">
         <v>330</v>
@@ -18417,7 +18420,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J513" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
@@ -18437,7 +18440,7 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F514" s="7">
         <v>330</v>
@@ -18485,7 +18488,7 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F516" s="7">
         <v>330</v>
@@ -18497,7 +18500,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I516" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J516" s="7">
         <v>457</v>
@@ -18520,7 +18523,7 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F517" s="7">
         <v>330</v>
@@ -18529,7 +18532,7 @@
         <v>131</v>
       </c>
       <c t="s" r="H517" s="8">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c t="s" r="I517" s="7">
         <v>93</v>
@@ -18540,7 +18543,7 @@
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
       <c t="s" r="M517" s="7">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="518" ht="14.25" customHeight="1">
@@ -18555,13 +18558,13 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F518" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G518" s="8">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c t="s" r="H518" s="8">
         <v>131</v>
@@ -18603,7 +18606,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F520" s="7">
         <v>330</v>
@@ -18615,7 +18618,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I520" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J520" s="7">
         <v>457</v>
@@ -18623,7 +18626,7 @@
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
       <c t="s" r="M520" s="7">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -18638,7 +18641,7 @@
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F521" s="7">
         <v>330</v>
@@ -18647,7 +18650,7 @@
         <v>131</v>
       </c>
       <c t="s" r="H521" s="8">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c t="s" r="I521" s="7">
         <v>19</v>
@@ -18658,7 +18661,7 @@
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
       <c t="s" r="M521" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="522" ht="14.25" customHeight="1">
@@ -18673,22 +18676,22 @@
       </c>
       <c r="D522" s="7"/>
       <c t="s" r="E522" s="7">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F522" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G522" s="8">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c t="s" r="H522" s="8">
         <v>131</v>
       </c>
       <c t="s" r="I522" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J522" s="7">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="K522" s="7"/>
       <c r="L522" s="7"/>
@@ -18721,7 +18724,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F524" s="7">
         <v>330</v>
@@ -18743,7 +18746,7 @@
       </c>
       <c r="L524" s="7"/>
       <c t="s" r="M524" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="525" ht="15" customHeight="1">
@@ -18758,7 +18761,7 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F525" s="7">
         <v>330</v>
@@ -18767,7 +18770,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H525" s="8">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c t="s" r="I525" s="7">
         <v>113</v>
@@ -18806,13 +18809,13 @@
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F527" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G527" s="8">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c t="s" r="H527" s="8">
         <v>16</v>
@@ -18841,7 +18844,7 @@
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F528" s="7">
         <v>330</v>
@@ -18893,7 +18896,7 @@
       </c>
       <c r="D530" s="7"/>
       <c t="s" r="E530" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F530" s="7">
         <v>330</v>
@@ -18902,18 +18905,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H530" s="8">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c t="s" r="I530" s="7">
         <v>198</v>
       </c>
       <c t="s" r="J530" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
       <c t="s" r="M530" s="7">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="531" ht="14.25" customHeight="1">
@@ -18928,13 +18931,13 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G531" s="8">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c t="s" r="H531" s="8">
         <v>16</v>
@@ -18951,7 +18954,7 @@
     </row>
     <row r="532" ht="15.75" customHeight="1">
       <c t="s" r="A532" s="9">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B532" s="9"/>
       <c r="C532" s="9"/>
@@ -18971,7 +18974,7 @@
     <row r="533" ht="65.25" customHeight="1"/>
     <row r="534" ht="16.5" customHeight="1">
       <c t="s" r="A534" s="10">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B534" s="10"/>
       <c r="C534" s="10"/>
@@ -18984,7 +18987,7 @@
       <c r="J534" s="10"/>
       <c r="K534" s="10"/>
       <c t="s" r="L534" s="11">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M534" s="11"/>
       <c r="N534" s="11"/>
